--- a/KatalonData/BWPBootstrapData/BWPCCData.xlsx
+++ b/KatalonData/BWPBootstrapData/BWPCCData.xlsx
@@ -52,7 +52,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="528" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="548" uniqueCount="87">
   <si>
     <t>Result</t>
   </si>
@@ -298,6 +298,21 @@
   </si>
   <si>
     <t>Fri Nov 21 00:30:17 IST 2025</t>
+  </si>
+  <si>
+    <t>Wed Dec 10 20:37:01 EST 2025</t>
+  </si>
+  <si>
+    <t>Wed Dec 10 20:38:06 EST 2025</t>
+  </si>
+  <si>
+    <t>Mon Dec 15 12:24:14 EST 2025</t>
+  </si>
+  <si>
+    <t>Mon Dec 15 12:31:52 EST 2025</t>
+  </si>
+  <si>
+    <t>Mon Dec 15 14:42:01 EST 2025</t>
   </si>
 </sst>
 </file>
@@ -687,7 +702,7 @@
         <v>22</v>
       </c>
       <c r="B2" t="s">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -2164,7 +2179,7 @@
         <v>22</v>
       </c>
       <c r="B2" t="s">
-        <v>62</v>
+        <v>83</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">

--- a/KatalonData/BWPBootstrapData/BWPCCData.xlsx
+++ b/KatalonData/BWPBootstrapData/BWPCCData.xlsx
@@ -1,42 +1,43 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29029"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29231"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <mc:AlternateContent>
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\t476046\Documents\VPS-Katalon-feature-VRelay\KatalonData\BWPBootstrapData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{47E44C90-C1EF-4204-BC2A-17B834AEEF75}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr documentId="13_ncr:1_{9E609A3C-EAF3-4D2D-8F1A-53C9CA74E6D2}" revIDLastSave="0" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView activeTab="3" windowHeight="12456" windowWidth="23256" xWindow="-108" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}" yWindow="-108"/>
   </bookViews>
   <sheets>
-    <sheet name="ModifyPaymentsCC1" sheetId="19" r:id="rId1"/>
-    <sheet name="ModifyPaymentsCC2" sheetId="20" r:id="rId2"/>
-    <sheet name="PayNowCCNoCF" sheetId="1" r:id="rId3"/>
-    <sheet name="PayNowCCNoCFReqFields" sheetId="2" r:id="rId4"/>
-    <sheet name="MissingReqFieldsCC" sheetId="18" r:id="rId5"/>
-    <sheet name="CardExpiredError" sheetId="10" r:id="rId6"/>
-    <sheet name="CardNotAcceptError" sheetId="11" r:id="rId7"/>
-    <sheet name="PayNowCCSCF" sheetId="3" r:id="rId8"/>
-    <sheet name="PayNowCCDCF" sheetId="4" r:id="rId9"/>
-    <sheet name="PayNowCCNoCFOnly" sheetId="5" r:id="rId10"/>
-    <sheet name="NoModifyAmountCC" sheetId="6" r:id="rId11"/>
-    <sheet name="MaxAmountErrorCC" sheetId="7" r:id="rId12"/>
-    <sheet name="MinAmountErrorCC" sheetId="8" r:id="rId13"/>
-    <sheet name="VerifyUDF9Error" sheetId="9" r:id="rId14"/>
-    <sheet name="DualCFCeilingCC" sheetId="12" r:id="rId15"/>
-    <sheet name="DualCFFlatCC" sheetId="13" r:id="rId16"/>
-    <sheet name="DualCFPercentageCC" sheetId="14" r:id="rId17"/>
-    <sheet name="SingleCFCeilingCC" sheetId="15" r:id="rId18"/>
-    <sheet name="SingleCFFlatCC" sheetId="16" r:id="rId19"/>
-    <sheet name="SingleCFPercentageCC" sheetId="17" r:id="rId20"/>
+    <sheet name="ModifyPaymentsCC1" r:id="rId1" sheetId="19"/>
+    <sheet name="ModifyPaymentsCC2" r:id="rId2" sheetId="20"/>
+    <sheet name="PayNowCCNoCF" r:id="rId3" sheetId="1"/>
+    <sheet name="ModifyAmountField" r:id="rId4" sheetId="21"/>
+    <sheet name="PayNowCCNoCFReqFields" r:id="rId5" sheetId="2"/>
+    <sheet name="MissingReqFieldsCC" r:id="rId6" sheetId="18"/>
+    <sheet name="CardExpiredError" r:id="rId7" sheetId="10"/>
+    <sheet name="CardNotAcceptError" r:id="rId8" sheetId="11"/>
+    <sheet name="PayNowCCSCF" r:id="rId9" sheetId="3"/>
+    <sheet name="PayNowCCDCF" r:id="rId10" sheetId="4"/>
+    <sheet name="PayNowCCNoCFOnly" r:id="rId11" sheetId="5"/>
+    <sheet name="NoModifyAmountCC" r:id="rId12" sheetId="6"/>
+    <sheet name="MaxAmountErrorCC" r:id="rId13" sheetId="7"/>
+    <sheet name="MinAmountErrorCC" r:id="rId14" sheetId="8"/>
+    <sheet name="VerifyUDF9Error" r:id="rId15" sheetId="9"/>
+    <sheet name="DualCFCeilingCC" r:id="rId16" sheetId="12"/>
+    <sheet name="DualCFFlatCC" r:id="rId17" sheetId="13"/>
+    <sheet name="DualCFPercentageCC" r:id="rId18" sheetId="14"/>
+    <sheet name="SingleCFCeilingCC" r:id="rId19" sheetId="15"/>
+    <sheet name="SingleCFFlatCC" r:id="rId20" sheetId="16"/>
+    <sheet name="SingleCFPercentageCC" r:id="rId21" sheetId="17"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+    <ext uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -55,7 +56,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="495" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1077" uniqueCount="199">
   <si>
     <t>Result</t>
   </si>
@@ -180,61 +181,485 @@
     <t>16</t>
   </si>
   <si>
-    <t>Thu Nov 20 22:52:08 IST 2025</t>
-  </si>
-  <si>
-    <t>Thu Nov 20 22:55:11 IST 2025</t>
-  </si>
-  <si>
-    <t>Thu Nov 20 23:07:35 IST 2025</t>
-  </si>
-  <si>
-    <t>Thu Nov 20 23:17:25 IST 2025</t>
-  </si>
-  <si>
-    <t>Thu Nov 20 23:21:58 IST 2025</t>
-  </si>
-  <si>
     <t>Thu Nov 20 23:35:41 IST 2025</t>
   </si>
   <si>
-    <t>Thu Nov 20 23:50:55 IST 2025</t>
-  </si>
-  <si>
-    <t>Thu Nov 20 23:55:23 IST 2025</t>
-  </si>
-  <si>
-    <t>Fri Nov 21 00:01:37 IST 2025</t>
-  </si>
-  <si>
-    <t>Fri Nov 21 00:20:51 IST 2025</t>
-  </si>
-  <si>
-    <t>Fri Nov 21 00:23:07 IST 2025</t>
-  </si>
-  <si>
-    <t>Fri Nov 21 00:23:38 IST 2025</t>
-  </si>
-  <si>
-    <t>Fri Nov 21 00:30:17 IST 2025</t>
-  </si>
-  <si>
-    <t>Fri Nov 21 19:11:15 IST 2025</t>
-  </si>
-  <si>
-    <t>Fri Nov 21 19:14:52 IST 2025</t>
-  </si>
-  <si>
-    <t>Fri Nov 21 21:27:44 IST 2025</t>
-  </si>
-  <si>
     <t>17</t>
+  </si>
+  <si>
+    <t>Wed Dec 10 01:28:41 IST 2025</t>
+  </si>
+  <si>
+    <t>Wed Dec 10 01:29:36 IST 2025</t>
+  </si>
+  <si>
+    <t>Wed Dec 10 01:30:20 IST 2025</t>
+  </si>
+  <si>
+    <t>Wed Dec 10 01:31:51 IST 2025</t>
+  </si>
+  <si>
+    <t>Wed Dec 10 01:39:00 IST 2025</t>
+  </si>
+  <si>
+    <t>Wed Dec 10 01:41:41 IST 2025</t>
+  </si>
+  <si>
+    <t>Wed Dec 10 01:44:26 IST 2025</t>
+  </si>
+  <si>
+    <t>Wed Dec 10 01:54:47 IST 2025</t>
+  </si>
+  <si>
+    <t>Wed Dec 10 01:57:47 IST 2025</t>
+  </si>
+  <si>
+    <t>Wed Dec 10 02:01:34 IST 2025</t>
+  </si>
+  <si>
+    <t>Wed Dec 10 02:05:40 IST 2025</t>
+  </si>
+  <si>
+    <t>Wed Dec 10 02:05:51 IST 2025</t>
+  </si>
+  <si>
+    <t>Wed Dec 10 02:06:55 IST 2025</t>
+  </si>
+  <si>
+    <t>Wed Dec 10 02:08:14 IST 2025</t>
+  </si>
+  <si>
+    <t>Wed Dec 10 02:08:33 IST 2025</t>
+  </si>
+  <si>
+    <t>11.5</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>Fri Dec 12 19:37:25 IST 2025</t>
+  </si>
+  <si>
+    <t>Fri Dec 12 19:44:29 IST 2025</t>
+  </si>
+  <si>
+    <t>Fri Dec 12 19:48:53 IST 2025</t>
+  </si>
+  <si>
+    <t>Fri Dec 12 19:50:30 IST 2025</t>
+  </si>
+  <si>
+    <t>Fri Dec 12 19:54:30 IST 2025</t>
+  </si>
+  <si>
+    <t>Mon Dec 15 16:08:10 IST 2025</t>
+  </si>
+  <si>
+    <t>Mon Dec 15 16:08:51 IST 2025</t>
+  </si>
+  <si>
+    <t>Mon Dec 15 16:09:35 IST 2025</t>
+  </si>
+  <si>
+    <t>Mon Dec 15 16:11:25 IST 2025</t>
+  </si>
+  <si>
+    <t>Mon Dec 15 16:17:21 IST 2025</t>
+  </si>
+  <si>
+    <t>Mon Dec 15 16:23:07 IST 2025</t>
+  </si>
+  <si>
+    <t>Mon Dec 15 16:27:53 IST 2025</t>
+  </si>
+  <si>
+    <t>Mon Dec 15 16:35:35 IST 2025</t>
+  </si>
+  <si>
+    <t>Mon Dec 15 16:41:11 IST 2025</t>
+  </si>
+  <si>
+    <t>Mon Dec 15 16:48:09 IST 2025</t>
+  </si>
+  <si>
+    <t>Mon Dec 15 16:52:12 IST 2025</t>
+  </si>
+  <si>
+    <t>Mon Dec 15 16:57:21 IST 2025</t>
+  </si>
+  <si>
+    <t>Mon Dec 15 16:59:06 IST 2025</t>
+  </si>
+  <si>
+    <t>Mon Dec 15 17:00:41 IST 2025</t>
+  </si>
+  <si>
+    <t>Mon Dec 15 17:02:45 IST 2025</t>
+  </si>
+  <si>
+    <t>Mon Dec 15 17:04:19 IST 2025</t>
+  </si>
+  <si>
+    <t>Mon Dec 15 17:29:42 IST 2025</t>
+  </si>
+  <si>
+    <t>Mon Dec 15 17:30:00 IST 2025</t>
+  </si>
+  <si>
+    <t>Mon Dec 15 17:30:22 IST 2025</t>
+  </si>
+  <si>
+    <t>Mon Dec 15 17:32:04 IST 2025</t>
+  </si>
+  <si>
+    <t>Mon Dec 15 17:37:16 IST 2025</t>
+  </si>
+  <si>
+    <t>Mon Dec 15 17:41:25 IST 2025</t>
+  </si>
+  <si>
+    <t>Mon Dec 15 17:44:53 IST 2025</t>
+  </si>
+  <si>
+    <t>Mon Dec 15 17:49:54 IST 2025</t>
+  </si>
+  <si>
+    <t>Mon Dec 15 17:53:42 IST 2025</t>
+  </si>
+  <si>
+    <t>Mon Dec 15 18:00:54 IST 2025</t>
+  </si>
+  <si>
+    <t>Mon Dec 15 18:04:26 IST 2025</t>
+  </si>
+  <si>
+    <t>Mon Dec 15 18:10:04 IST 2025</t>
+  </si>
+  <si>
+    <t>Mon Dec 15 18:17:02 IST 2025</t>
+  </si>
+  <si>
+    <t>Mon Dec 15 18:17:32 IST 2025</t>
+  </si>
+  <si>
+    <t>Mon Dec 15 18:18:00 IST 2025</t>
+  </si>
+  <si>
+    <t>Mon Dec 15 18:18:26 IST 2025</t>
+  </si>
+  <si>
+    <t>Mon Dec 15 18:22:45 IST 2025</t>
+  </si>
+  <si>
+    <t>Mon Dec 15 19:31:19 IST 2025</t>
+  </si>
+  <si>
+    <t>Mon Dec 15 19:32:27 IST 2025</t>
+  </si>
+  <si>
+    <t>Mon Dec 15 20:05:35 IST 2025</t>
+  </si>
+  <si>
+    <t>Mon Dec 15 20:11:50 IST 2025</t>
+  </si>
+  <si>
+    <t>Mon Dec 15 20:16:34 IST 2025</t>
+  </si>
+  <si>
+    <t>Mon Dec 15 20:24:56 IST 2025</t>
+  </si>
+  <si>
+    <t>Mon Dec 15 20:26:27 IST 2025</t>
+  </si>
+  <si>
+    <t>Mon Dec 15 20:40:22 IST 2025</t>
+  </si>
+  <si>
+    <t>Mon Dec 15 20:50:28 IST 2025</t>
+  </si>
+  <si>
+    <t>Mon Dec 15 20:53:01 IST 2025</t>
+  </si>
+  <si>
+    <t>Mon Dec 15 21:15:43 IST 2025</t>
+  </si>
+  <si>
+    <t>Mon Dec 15 21:24:50 IST 2025</t>
+  </si>
+  <si>
+    <t>Mon Dec 15 21:36:44 IST 2025</t>
+  </si>
+  <si>
+    <t>Mon Dec 15 21:41:06 IST 2025</t>
+  </si>
+  <si>
+    <t>Mon Dec 15 22:36:14 IST 2025</t>
+  </si>
+  <si>
+    <t>Mon Dec 15 22:37:58 IST 2025</t>
+  </si>
+  <si>
+    <t>Tue Dec 16 21:19:16 IST 2025</t>
+  </si>
+  <si>
+    <t>Tue Dec 16 21:20:01 IST 2025</t>
+  </si>
+  <si>
+    <t>Tue Dec 16 21:20:35 IST 2025</t>
+  </si>
+  <si>
+    <t>Tue Dec 16 21:22:10 IST 2025</t>
+  </si>
+  <si>
+    <t>Tue Dec 16 21:27:51 IST 2025</t>
+  </si>
+  <si>
+    <t>Tue Dec 16 21:30:00 IST 2025</t>
+  </si>
+  <si>
+    <t>Tue Dec 16 21:32:41 IST 2025</t>
+  </si>
+  <si>
+    <t>Tue Dec 16 21:37:18 IST 2025</t>
+  </si>
+  <si>
+    <t>Tue Dec 16 21:39:14 IST 2025</t>
+  </si>
+  <si>
+    <t>Tue Dec 16 21:43:16 IST 2025</t>
+  </si>
+  <si>
+    <t>Tue Dec 16 21:57:50 IST 2025</t>
+  </si>
+  <si>
+    <t>Tue Dec 16 22:03:06 IST 2025</t>
+  </si>
+  <si>
+    <t>Tue Dec 16 22:03:37 IST 2025</t>
+  </si>
+  <si>
+    <t>Tue Dec 16 22:05:18 IST 2025</t>
+  </si>
+  <si>
+    <t>Tue Dec 16 22:06:13 IST 2025</t>
+  </si>
+  <si>
+    <t>Tue Dec 16 22:07:46 IST 2025</t>
+  </si>
+  <si>
+    <t>Tue Dec 16 22:35:31 IST 2025</t>
+  </si>
+  <si>
+    <t>Tue Dec 16 22:35:56 IST 2025</t>
+  </si>
+  <si>
+    <t>Tue Dec 16 22:36:19 IST 2025</t>
+  </si>
+  <si>
+    <t>Tue Dec 16 22:37:53 IST 2025</t>
+  </si>
+  <si>
+    <t>Tue Dec 16 22:44:22 IST 2025</t>
+  </si>
+  <si>
+    <t>Tue Dec 16 22:50:48 IST 2025</t>
+  </si>
+  <si>
+    <t>Tue Dec 16 22:57:32 IST 2025</t>
+  </si>
+  <si>
+    <t>Tue Dec 16 23:03:15 IST 2025</t>
+  </si>
+  <si>
+    <t>Tue Dec 16 23:06:45 IST 2025</t>
+  </si>
+  <si>
+    <t>Tue Dec 16 23:10:46 IST 2025</t>
+  </si>
+  <si>
+    <t>Tue Dec 16 23:14:00 IST 2025</t>
+  </si>
+  <si>
+    <t>Tue Dec 16 23:17:40 IST 2025</t>
+  </si>
+  <si>
+    <t>Tue Dec 16 23:22:36 IST 2025</t>
+  </si>
+  <si>
+    <t>Tue Dec 16 23:24:18 IST 2025</t>
+  </si>
+  <si>
+    <t>Tue Dec 16 23:25:55 IST 2025</t>
+  </si>
+  <si>
+    <t>Tue Dec 16 23:26:29 IST 2025</t>
+  </si>
+  <si>
+    <t>Tue Dec 16 23:27:00 IST 2025</t>
+  </si>
+  <si>
+    <t>Wed Dec 17 02:02:00 IST 2025</t>
+  </si>
+  <si>
+    <t>Wed Dec 17 02:02:24 IST 2025</t>
+  </si>
+  <si>
+    <t>Wed Dec 17 02:02:47 IST 2025</t>
+  </si>
+  <si>
+    <t>Wed Dec 17 02:04:21 IST 2025</t>
+  </si>
+  <si>
+    <t>Wed Dec 17 02:09:49 IST 2025</t>
+  </si>
+  <si>
+    <t>Wed Dec 17 02:13:02 IST 2025</t>
+  </si>
+  <si>
+    <t>Wed Dec 17 02:17:39 IST 2025</t>
+  </si>
+  <si>
+    <t>Wed Dec 17 02:24:19 IST 2025</t>
+  </si>
+  <si>
+    <t>Wed Dec 17 02:30:28 IST 2025</t>
+  </si>
+  <si>
+    <t>Wed Dec 17 02:33:59 IST 2025</t>
+  </si>
+  <si>
+    <t>Wed Dec 17 02:39:04 IST 2025</t>
+  </si>
+  <si>
+    <t>Wed Dec 17 02:46:14 IST 2025</t>
+  </si>
+  <si>
+    <t>Wed Dec 17 02:48:01 IST 2025</t>
+  </si>
+  <si>
+    <t>Wed Dec 17 02:49:40 IST 2025</t>
+  </si>
+  <si>
+    <t>Wed Dec 17 02:51:10 IST 2025</t>
+  </si>
+  <si>
+    <t>Wed Dec 17 02:52:39 IST 2025</t>
+  </si>
+  <si>
+    <t>Wed Dec 17 03:17:29 IST 2025</t>
+  </si>
+  <si>
+    <t>Wed Dec 17 03:17:54 IST 2025</t>
+  </si>
+  <si>
+    <t>Wed Dec 17 03:18:16 IST 2025</t>
+  </si>
+  <si>
+    <t>Wed Dec 17 03:19:50 IST 2025</t>
+  </si>
+  <si>
+    <t>Wed Dec 17 03:25:37 IST 2025</t>
+  </si>
+  <si>
+    <t>Wed Dec 17 03:30:23 IST 2025</t>
+  </si>
+  <si>
+    <t>Wed Dec 17 03:37:02 IST 2025</t>
+  </si>
+  <si>
+    <t>Wed Dec 17 03:44:21 IST 2025</t>
+  </si>
+  <si>
+    <t>Wed Dec 17 03:48:04 IST 2025</t>
+  </si>
+  <si>
+    <t>Wed Dec 17 03:51:59 IST 2025</t>
+  </si>
+  <si>
+    <t>Wed Dec 17 03:57:34 IST 2025</t>
+  </si>
+  <si>
+    <t>Wed Dec 17 04:03:33 IST 2025</t>
+  </si>
+  <si>
+    <t>Wed Dec 17 04:06:33 IST 2025</t>
+  </si>
+  <si>
+    <t>Wed Dec 17 04:09:14 IST 2025</t>
+  </si>
+  <si>
+    <t>Wed Dec 17 04:09:38 IST 2025</t>
+  </si>
+  <si>
+    <t>Wed Dec 17 04:10:59 IST 2025</t>
+  </si>
+  <si>
+    <t>Wed Dec 17 04:12:30 IST 2025</t>
+  </si>
+  <si>
+    <t>Wed Dec 17 12:42:39 IST 2025</t>
+  </si>
+  <si>
+    <t>Wed Dec 17 12:43:13 IST 2025</t>
+  </si>
+  <si>
+    <t>Wed Dec 17 12:43:36 IST 2025</t>
+  </si>
+  <si>
+    <t>Wed Dec 17 12:45:23 IST 2025</t>
+  </si>
+  <si>
+    <t>Wed Dec 17 12:50:59 IST 2025</t>
+  </si>
+  <si>
+    <t>Wed Dec 17 12:56:41 IST 2025</t>
+  </si>
+  <si>
+    <t>Wed Dec 17 13:00:15 IST 2025</t>
+  </si>
+  <si>
+    <t>Wed Dec 17 13:05:13 IST 2025</t>
+  </si>
+  <si>
+    <t>Wed Dec 17 13:11:37 IST 2025</t>
+  </si>
+  <si>
+    <t>Wed Dec 17 13:18:18 IST 2025</t>
+  </si>
+  <si>
+    <t>Wed Dec 17 19:50:15 IST 2025</t>
+  </si>
+  <si>
+    <t>Wed Dec 17 19:50:36 IST 2025</t>
+  </si>
+  <si>
+    <t>Wed Dec 17 19:51:03 IST 2025</t>
+  </si>
+  <si>
+    <t>Wed Dec 17 19:52:29 IST 2025</t>
+  </si>
+  <si>
+    <t>Wed Dec 17 19:57:23 IST 2025</t>
+  </si>
+  <si>
+    <t>Wed Dec 17 20:01:31 IST 2025</t>
+  </si>
+  <si>
+    <t>Wed Dec 17 20:05:33 IST 2025</t>
+  </si>
+  <si>
+    <t>Wed Dec 17 20:10:50 IST 2025</t>
+  </si>
+  <si>
+    <t>Tue Jan 06 21:43:10 IST 2026</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="0"/>
   <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -277,20 +702,20 @@
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf borderId="0" fillId="0" fontId="0" numFmtId="0"/>
   </cellStyleXfs>
   <cellXfs count="3">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0"/>
+    <xf applyAlignment="1" applyBorder="1" applyNumberFormat="1" borderId="1" fillId="0" fontId="0" numFmtId="49" xfId="0">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf applyBorder="1" applyNumberFormat="1" borderId="1" fillId="0" fontId="0" numFmtId="49" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle builtinId="0" name="Normal" xfId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <tableStyles count="0" defaultPivotStyle="PivotStyleLight16" defaultTableStyle="TableStyleMedium2"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -307,10 +732,10 @@
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
-        <a:sysClr val="windowText" lastClr="000000"/>
+        <a:sysClr lastClr="000000" val="windowText"/>
       </a:dk1>
       <a:lt1>
-        <a:sysClr val="window" lastClr="FFFFFF"/>
+        <a:sysClr lastClr="FFFFFF" val="window"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="44546A"/>
@@ -345,7 +770,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
+        <a:latin panose="020F0302020204030204" typeface="Calibri Light"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック Light"/>
@@ -380,7 +805,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin panose="020F0502020204030204" typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック"/>
@@ -474,21 +899,21 @@
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln algn="ctr" cap="flat" cmpd="sng" w="6350">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
           <a:miter lim="800000"/>
         </a:ln>
-        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln algn="ctr" cap="flat" cmpd="sng" w="12700">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
           <a:miter lim="800000"/>
         </a:ln>
-        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln algn="ctr" cap="flat" cmpd="sng" w="19050">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
@@ -505,7 +930,7 @@
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+            <a:outerShdw algn="ctr" blurRad="57150" dir="5400000" dist="19050" rotWithShape="0">
               <a:srgbClr val="000000">
                 <a:alpha val="63000"/>
               </a:srgbClr>
@@ -557,18 +982,18 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" name="Office Theme" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7A8F394B-F089-4FB3-82A1-125786B1E619}">
-  <dimension ref="A1:N2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7A8F394B-F089-4FB3-82A1-125786B1E619}">
+  <dimension ref="A1:O2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+    <row ht="28.8" r="1" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -645,16 +1070,16 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BBE94437-153A-41B2-A46E-2F45E61989DF}">
-  <dimension ref="A1:N2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{125BE3DD-7AC0-404A-8C39-EB8ECFFFBDDD}">
+  <dimension ref="A1:O2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+    <row ht="28.8" r="1" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -700,20 +1125,20 @@
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="B2" t="s">
-        <v>52</v>
+        <v>175</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
         <v>14</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="G2" s="1" t="s">
         <v>21</v>
@@ -726,7 +1151,7 @@
         <v>16</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="L2" s="1"/>
       <c r="M2" s="1" t="s">
@@ -737,16 +1162,16 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{093A05D5-CD46-4FC8-83C2-DE55EC3B00E1}">
-  <dimension ref="A1:N2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BBE94437-153A-41B2-A46E-2F45E61989DF}">
+  <dimension ref="A1:O2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+    <row ht="28.8" r="1" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -792,20 +1217,20 @@
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="B2" t="s">
-        <v>46</v>
+        <v>177</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
         <v>14</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G2" s="1" t="s">
         <v>21</v>
@@ -829,16 +1254,16 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2A6F3014-83EE-40CF-BEA6-9E7A762354AA}">
-  <dimension ref="A1:N2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{093A05D5-CD46-4FC8-83C2-DE55EC3B00E1}">
+  <dimension ref="A1:O2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+    <row ht="28.8" r="1" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -884,20 +1309,20 @@
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="B2" t="s">
-        <v>54</v>
+        <v>197</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
         <v>14</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="G2" s="1" t="s">
         <v>21</v>
@@ -921,16 +1346,16 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{434CAF96-FDCD-425D-B74E-26C08061546A}">
-  <dimension ref="A1:N2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2A6F3014-83EE-40CF-BEA6-9E7A762354AA}">
+  <dimension ref="A1:O2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+    <row ht="28.8" r="1" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -979,14 +1404,14 @@
         <v>22</v>
       </c>
       <c r="B2" t="s">
-        <v>42</v>
+        <v>192</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
         <v>14</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>33</v>
+        <v>23</v>
       </c>
       <c r="F2" s="1" t="s">
         <v>20</v>
@@ -1013,16 +1438,16 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{87175E7B-348C-48F8-975E-573E1AA57C35}">
-  <dimension ref="A1:N2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{434CAF96-FDCD-425D-B74E-26C08061546A}">
+  <dimension ref="A1:O2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+    <row ht="28.8" r="1" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1068,17 +1493,17 @@
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="B2" t="s">
-        <v>32</v>
+        <v>193</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
         <v>14</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="F2" s="1" t="s">
         <v>20</v>
@@ -1105,16 +1530,16 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FF76F2B3-5F15-409A-AC34-86B0DD8FC5F1}">
-  <dimension ref="A1:N2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{87175E7B-348C-48F8-975E-573E1AA57C35}">
+  <dimension ref="A1:O2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+    <row ht="28.8" r="1" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1160,20 +1585,20 @@
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="B2" t="s">
-        <v>43</v>
+        <v>32</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
         <v>14</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="G2" s="1" t="s">
         <v>21</v>
@@ -1197,16 +1622,16 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0BF1CC49-076D-4B64-8F44-11F5FA5C3B7C}">
-  <dimension ref="A1:N2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FF76F2B3-5F15-409A-AC34-86B0DD8FC5F1}">
+  <dimension ref="A1:O2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+    <row ht="28.8" r="1" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1252,17 +1677,17 @@
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="B2" t="s">
-        <v>44</v>
+        <v>194</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
         <v>14</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F2" s="1" t="s">
         <v>25</v>
@@ -1278,7 +1703,7 @@
         <v>16</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="L2" s="1"/>
       <c r="M2" s="1" t="s">
@@ -1289,16 +1714,16 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D2A016DD-A4BF-47A4-99DE-0B94685F9A61}">
-  <dimension ref="A1:N2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0BF1CC49-076D-4B64-8F44-11F5FA5C3B7C}">
+  <dimension ref="A1:O2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+    <row ht="28.8" r="1" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1344,17 +1769,17 @@
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="B2" t="s">
-        <v>45</v>
+        <v>195</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
         <v>14</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F2" s="1" t="s">
         <v>25</v>
@@ -1381,16 +1806,16 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3D4D6FED-07DF-4BD9-BB91-007F4EF89576}">
-  <dimension ref="A1:N2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D2A016DD-A4BF-47A4-99DE-0B94685F9A61}">
+  <dimension ref="A1:O2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+    <row ht="28.8" r="1" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1439,17 +1864,17 @@
         <v>22</v>
       </c>
       <c r="B2" t="s">
-        <v>47</v>
+        <v>196</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
         <v>14</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G2" s="1" t="s">
         <v>21</v>
@@ -1462,7 +1887,7 @@
         <v>16</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="L2" s="1"/>
       <c r="M2" s="1" t="s">
@@ -1473,16 +1898,16 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{28EE865A-189F-47E2-B372-099EB34B0721}">
-  <dimension ref="A1:N2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3D4D6FED-07DF-4BD9-BB91-007F4EF89576}">
+  <dimension ref="A1:O2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+    <row ht="28.8" r="1" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1528,17 +1953,17 @@
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="B2" t="s">
-        <v>48</v>
+        <v>188</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
         <v>14</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F2" s="1" t="s">
         <v>24</v>
@@ -1554,7 +1979,7 @@
         <v>16</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="L2" s="1"/>
       <c r="M2" s="1" t="s">
@@ -1565,16 +1990,16 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E6E76688-C590-48CE-8843-48B79B2A30B7}">
-  <dimension ref="A1:N2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E6E76688-C590-48CE-8843-48B79B2A30B7}">
+  <dimension ref="A1:O2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+    <row ht="28.8" r="1" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1651,16 +2076,108 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B29E0A75-769C-43A6-A3D3-703A1A1AFA44}">
-  <dimension ref="A1:N2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{28EE865A-189F-47E2-B372-099EB34B0721}">
+  <dimension ref="A1:O2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+    <row ht="28.8" r="1" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B2" t="s">
+        <v>189</v>
+      </c>
+      <c r="C2" s="2"/>
+      <c r="D2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="H2" s="1"/>
+      <c r="I2" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="L2" s="1"/>
+      <c r="M2" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="N2" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B29E0A75-769C-43A6-A3D3-703A1A1AFA44}">
+  <dimension ref="A1:O2"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row ht="28.8" r="1" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1709,7 +2226,7 @@
         <v>22</v>
       </c>
       <c r="B2" t="s">
-        <v>49</v>
+        <v>174</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -1743,16 +2260,16 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:N2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:O2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+    <row ht="28.8" r="1" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1801,7 +2318,7 @@
         <v>22</v>
       </c>
       <c r="B2" t="s">
-        <v>51</v>
+        <v>176</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -1835,7 +2352,7 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
   <headerFooter>
     <oddFooter xml:space="preserve">&amp;C_x000D_&amp;1#&amp;"Calibri"&amp;10&amp;K000000 Public </oddFooter>
   </headerFooter>
@@ -1843,14 +2360,11 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2B2AA229-8633-483E-A009-0064BA327142}">
-  <dimension ref="A1:N2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9F43C6F9-1E8C-46BC-A704-23D3CEBA418B}">
+  <dimension ref="A1:O2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="3" max="3" width="27.77734375" customWidth="1" collapsed="1"/>
-  </cols>
   <sheetData>
-    <row r="1" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+    <row ht="28.8" r="1" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1896,17 +2410,17 @@
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="B2" t="s">
-        <v>56</v>
+        <v>170</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
         <v>14</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>34</v>
+        <v>15</v>
       </c>
       <c r="F2" s="1" t="s">
         <v>20</v>
@@ -1915,7 +2429,7 @@
         <v>21</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>26</v>
+        <v>58</v>
       </c>
       <c r="I2" s="1" t="s">
         <v>17</v>
@@ -1928,23 +2442,120 @@
       </c>
       <c r="L2" s="1"/>
       <c r="M2" s="1" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E49D1CA0-9ECE-4C77-A64C-43CA3156CCD7}">
-  <dimension ref="A1:N2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2B2AA229-8633-483E-A009-0064BA327142}">
+  <dimension ref="A1:O2"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="3" max="3" customWidth="true" width="27.77734375" collapsed="true"/>
+  </cols>
+  <sheetData>
+    <row ht="28.8" r="1" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B2" t="s">
+        <v>178</v>
+      </c>
+      <c r="C2" s="2"/>
+      <c r="D2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="L2" s="1"/>
+      <c r="M2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="N2" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E49D1CA0-9ECE-4C77-A64C-43CA3156CCD7}">
+  <dimension ref="A1:O2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+    <row ht="28.8" r="1" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1994,7 +2605,7 @@
         <v>14</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>57</v>
+        <v>42</v>
       </c>
       <c r="F2" s="1" t="s">
         <v>20</v>
@@ -2021,108 +2632,16 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EF4DDCDE-4C11-464F-9492-FC8FE5D5A265}">
-  <dimension ref="A1:N2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <sheetData>
-    <row r="1" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="N1" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>22</v>
-      </c>
-      <c r="B2" t="s">
-        <v>41</v>
-      </c>
-      <c r="C2" s="2"/>
-      <c r="D2" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="G2" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="H2" s="1"/>
-      <c r="I2" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="J2" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="K2" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="L2" s="1"/>
-      <c r="M2" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="N2" s="1" t="s">
-        <v>19</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{61EC5E6A-6755-4451-A097-7A8CEE1F522B}">
-  <dimension ref="A1:N2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EF4DDCDE-4C11-464F-9492-FC8FE5D5A265}">
+  <dimension ref="A1:O2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+    <row ht="28.8" r="1" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2171,7 +2690,7 @@
         <v>22</v>
       </c>
       <c r="B2" t="s">
-        <v>55</v>
+        <v>190</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -2205,16 +2724,16 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{46BFFB65-1565-4A34-B0E7-464EF87C75A7}">
-  <dimension ref="A1:N2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{61EC5E6A-6755-4451-A097-7A8CEE1F522B}">
+  <dimension ref="A1:O2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+    <row ht="28.8" r="1" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2263,17 +2782,17 @@
         <v>22</v>
       </c>
       <c r="B2" t="s">
-        <v>53</v>
+        <v>191</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
         <v>14</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="G2" s="1" t="s">
         <v>21</v>
@@ -2286,7 +2805,7 @@
         <v>16</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>15</v>
+        <v>34</v>
       </c>
       <c r="L2" s="1"/>
       <c r="M2" s="1" t="s">
@@ -2297,16 +2816,16 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{125BE3DD-7AC0-404A-8C39-EB8ECFFFBDDD}">
-  <dimension ref="A1:N2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{46BFFB65-1565-4A34-B0E7-464EF87C75A7}">
+  <dimension ref="A1:O2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+    <row ht="28.8" r="1" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2352,20 +2871,20 @@
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="B2" t="s">
-        <v>50</v>
+        <v>198</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
         <v>14</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G2" s="1" t="s">
         <v>21</v>
@@ -2389,6 +2908,6 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
 </file>
--- a/KatalonData/BWPBootstrapData/BWPCCData.xlsx
+++ b/KatalonData/BWPBootstrapData/BWPCCData.xlsx
@@ -1,42 +1,42 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29029"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <mc:AlternateContent>
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\t476046\Documents\VPS-Katalon-feature-VRelay\KatalonData\BWPBootstrapData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{47E44C90-C1EF-4204-BC2A-17B834AEEF75}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr documentId="13_ncr:1_{4CA609CD-4DB6-4AB2-96AB-BEF318A8DD1A}" revIDLastSave="0" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView activeTab="1" windowHeight="9000" windowWidth="17280" xWindow="1500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}" yWindow="1500"/>
   </bookViews>
   <sheets>
-    <sheet name="ModifyPaymentsCC1" sheetId="19" r:id="rId1"/>
-    <sheet name="ModifyPaymentsCC2" sheetId="20" r:id="rId2"/>
-    <sheet name="PayNowCCNoCF" sheetId="1" r:id="rId3"/>
-    <sheet name="PayNowCCNoCFReqFields" sheetId="2" r:id="rId4"/>
-    <sheet name="MissingReqFieldsCC" sheetId="18" r:id="rId5"/>
-    <sheet name="CardExpiredError" sheetId="10" r:id="rId6"/>
-    <sheet name="CardNotAcceptError" sheetId="11" r:id="rId7"/>
-    <sheet name="PayNowCCSCF" sheetId="3" r:id="rId8"/>
-    <sheet name="PayNowCCDCF" sheetId="4" r:id="rId9"/>
-    <sheet name="PayNowCCNoCFOnly" sheetId="5" r:id="rId10"/>
-    <sheet name="NoModifyAmountCC" sheetId="6" r:id="rId11"/>
-    <sheet name="MaxAmountErrorCC" sheetId="7" r:id="rId12"/>
-    <sheet name="MinAmountErrorCC" sheetId="8" r:id="rId13"/>
-    <sheet name="VerifyUDF9Error" sheetId="9" r:id="rId14"/>
-    <sheet name="DualCFCeilingCC" sheetId="12" r:id="rId15"/>
-    <sheet name="DualCFFlatCC" sheetId="13" r:id="rId16"/>
-    <sheet name="DualCFPercentageCC" sheetId="14" r:id="rId17"/>
-    <sheet name="SingleCFCeilingCC" sheetId="15" r:id="rId18"/>
-    <sheet name="SingleCFFlatCC" sheetId="16" r:id="rId19"/>
-    <sheet name="SingleCFPercentageCC" sheetId="17" r:id="rId20"/>
+    <sheet name="ModifyPaymentsCC1" r:id="rId1" sheetId="19"/>
+    <sheet name="ModifyPaymentsCC2" r:id="rId2" sheetId="20"/>
+    <sheet name="PayNowCCNoCF" r:id="rId3" sheetId="1"/>
+    <sheet name="PayNowCCNoCFReqFields" r:id="rId4" sheetId="2"/>
+    <sheet name="MissingReqFieldsCC" r:id="rId5" sheetId="18"/>
+    <sheet name="CardExpiredError" r:id="rId6" sheetId="10"/>
+    <sheet name="CardNotAcceptError" r:id="rId7" sheetId="11"/>
+    <sheet name="PayNowCCSCF" r:id="rId8" sheetId="3"/>
+    <sheet name="PayNowCCDCF" r:id="rId9" sheetId="4"/>
+    <sheet name="PayNowCCNoCFOnly" r:id="rId10" sheetId="5"/>
+    <sheet name="NoModifyAmountCC" r:id="rId11" sheetId="6"/>
+    <sheet name="MaxAmountErrorCC" r:id="rId12" sheetId="7"/>
+    <sheet name="MinAmountErrorCC" r:id="rId13" sheetId="8"/>
+    <sheet name="VerifyUDF9Error" r:id="rId14" sheetId="9"/>
+    <sheet name="DualCFCeilingCC" r:id="rId15" sheetId="12"/>
+    <sheet name="DualCFFlatCC" r:id="rId16" sheetId="13"/>
+    <sheet name="DualCFPercentageCC" r:id="rId17" sheetId="14"/>
+    <sheet name="SingleCFCeilingCC" r:id="rId18" sheetId="15"/>
+    <sheet name="SingleCFFlatCC" r:id="rId19" sheetId="16"/>
+    <sheet name="SingleCFPercentageCC" r:id="rId20" sheetId="17"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+    <ext uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -55,7 +55,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="495" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="499" uniqueCount="60">
   <si>
     <t>Result</t>
   </si>
@@ -180,61 +180,68 @@
     <t>16</t>
   </si>
   <si>
-    <t>Thu Nov 20 22:52:08 IST 2025</t>
-  </si>
-  <si>
-    <t>Thu Nov 20 22:55:11 IST 2025</t>
-  </si>
-  <si>
-    <t>Thu Nov 20 23:07:35 IST 2025</t>
-  </si>
-  <si>
-    <t>Thu Nov 20 23:17:25 IST 2025</t>
-  </si>
-  <si>
-    <t>Thu Nov 20 23:21:58 IST 2025</t>
-  </si>
-  <si>
-    <t>Thu Nov 20 23:35:41 IST 2025</t>
-  </si>
-  <si>
-    <t>Thu Nov 20 23:50:55 IST 2025</t>
-  </si>
-  <si>
-    <t>Thu Nov 20 23:55:23 IST 2025</t>
-  </si>
-  <si>
-    <t>Fri Nov 21 00:01:37 IST 2025</t>
-  </si>
-  <si>
-    <t>Fri Nov 21 00:20:51 IST 2025</t>
-  </si>
-  <si>
-    <t>Fri Nov 21 00:23:07 IST 2025</t>
-  </si>
-  <si>
-    <t>Fri Nov 21 00:23:38 IST 2025</t>
-  </si>
-  <si>
-    <t>Fri Nov 21 00:30:17 IST 2025</t>
-  </si>
-  <si>
-    <t>Fri Nov 21 19:11:15 IST 2025</t>
-  </si>
-  <si>
-    <t>Fri Nov 21 19:14:52 IST 2025</t>
-  </si>
-  <si>
-    <t>Fri Nov 21 21:27:44 IST 2025</t>
-  </si>
-  <si>
     <t>17</t>
+  </si>
+  <si>
+    <t>Sat Jan 17 01:51:55 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Jan 17 01:52:58 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Jan 17 02:02:45 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Jan 17 02:09:01 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Jan 17 02:12:22 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Jan 17 02:30:44 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Jan 17 02:34:41 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Jan 17 02:38:38 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Jan 17 02:41:02 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Jan 17 02:43:28 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Jan 17 02:46:46 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Jan 17 02:47:13 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Jan 17 02:51:57 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Jan 17 02:55:23 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Jan 19 19:30:33 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Jan 19 19:31:39 IST 2026</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>Mon Jan 19 20:07:13 IST 2026</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="0"/>
   <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -277,20 +284,20 @@
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf borderId="0" fillId="0" fontId="0" numFmtId="0"/>
   </cellStyleXfs>
   <cellXfs count="3">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0"/>
+    <xf applyAlignment="1" applyBorder="1" applyNumberFormat="1" borderId="1" fillId="0" fontId="0" numFmtId="49" xfId="0">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf applyBorder="1" applyNumberFormat="1" borderId="1" fillId="0" fontId="0" numFmtId="49" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle builtinId="0" name="Normal" xfId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <tableStyles count="0" defaultPivotStyle="PivotStyleLight16" defaultTableStyle="TableStyleMedium2"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -307,10 +314,10 @@
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
-        <a:sysClr val="windowText" lastClr="000000"/>
+        <a:sysClr lastClr="000000" val="windowText"/>
       </a:dk1>
       <a:lt1>
-        <a:sysClr val="window" lastClr="FFFFFF"/>
+        <a:sysClr lastClr="FFFFFF" val="window"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="44546A"/>
@@ -345,7 +352,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
+        <a:latin panose="020F0302020204030204" typeface="Calibri Light"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック Light"/>
@@ -380,7 +387,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin panose="020F0502020204030204" typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック"/>
@@ -474,21 +481,21 @@
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln algn="ctr" cap="flat" cmpd="sng" w="6350">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
           <a:miter lim="800000"/>
         </a:ln>
-        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln algn="ctr" cap="flat" cmpd="sng" w="12700">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
           <a:miter lim="800000"/>
         </a:ln>
-        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln algn="ctr" cap="flat" cmpd="sng" w="19050">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
@@ -505,7 +512,7 @@
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+            <a:outerShdw algn="ctr" blurRad="57150" dir="5400000" dist="19050" rotWithShape="0">
               <a:srgbClr val="000000">
                 <a:alpha val="63000"/>
               </a:srgbClr>
@@ -557,18 +564,18 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" name="Office Theme" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7A8F394B-F089-4FB3-82A1-125786B1E619}">
-  <dimension ref="A1:N2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7A8F394B-F089-4FB3-82A1-125786B1E619}">
+  <dimension ref="A1:O2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+    <row ht="28.8" r="1" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -645,16 +652,16 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BBE94437-153A-41B2-A46E-2F45E61989DF}">
-  <dimension ref="A1:N2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BBE94437-153A-41B2-A46E-2F45E61989DF}">
+  <dimension ref="A1:O2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+    <row ht="28.8" r="1" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -703,7 +710,7 @@
         <v>22</v>
       </c>
       <c r="B2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -737,16 +744,16 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{093A05D5-CD46-4FC8-83C2-DE55EC3B00E1}">
-  <dimension ref="A1:N2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{093A05D5-CD46-4FC8-83C2-DE55EC3B00E1}">
+  <dimension ref="A1:O2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+    <row ht="28.8" r="1" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -795,7 +802,7 @@
         <v>22</v>
       </c>
       <c r="B2" t="s">
-        <v>46</v>
+        <v>59</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -829,16 +836,16 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2A6F3014-83EE-40CF-BEA6-9E7A762354AA}">
-  <dimension ref="A1:N2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2A6F3014-83EE-40CF-BEA6-9E7A762354AA}">
+  <dimension ref="A1:O2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+    <row ht="28.8" r="1" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -887,7 +894,7 @@
         <v>22</v>
       </c>
       <c r="B2" t="s">
-        <v>54</v>
+        <v>42</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -921,16 +928,16 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{434CAF96-FDCD-425D-B74E-26C08061546A}">
-  <dimension ref="A1:N2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{434CAF96-FDCD-425D-B74E-26C08061546A}">
+  <dimension ref="A1:O2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+    <row ht="28.8" r="1" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -979,7 +986,7 @@
         <v>22</v>
       </c>
       <c r="B2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -1013,16 +1020,16 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{87175E7B-348C-48F8-975E-573E1AA57C35}">
-  <dimension ref="A1:N2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{87175E7B-348C-48F8-975E-573E1AA57C35}">
+  <dimension ref="A1:O2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+    <row ht="28.8" r="1" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1105,16 +1112,16 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FF76F2B3-5F15-409A-AC34-86B0DD8FC5F1}">
-  <dimension ref="A1:N2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FF76F2B3-5F15-409A-AC34-86B0DD8FC5F1}">
+  <dimension ref="A1:O2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+    <row ht="28.8" r="1" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1163,7 +1170,7 @@
         <v>22</v>
       </c>
       <c r="B2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -1197,16 +1204,16 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0BF1CC49-076D-4B64-8F44-11F5FA5C3B7C}">
-  <dimension ref="A1:N2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0BF1CC49-076D-4B64-8F44-11F5FA5C3B7C}">
+  <dimension ref="A1:O2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+    <row ht="28.8" r="1" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1255,7 +1262,7 @@
         <v>22</v>
       </c>
       <c r="B2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -1289,16 +1296,16 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D2A016DD-A4BF-47A4-99DE-0B94685F9A61}">
-  <dimension ref="A1:N2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D2A016DD-A4BF-47A4-99DE-0B94685F9A61}">
+  <dimension ref="A1:O2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+    <row ht="28.8" r="1" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1347,7 +1354,7 @@
         <v>22</v>
       </c>
       <c r="B2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -1381,16 +1388,16 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3D4D6FED-07DF-4BD9-BB91-007F4EF89576}">
-  <dimension ref="A1:N2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3D4D6FED-07DF-4BD9-BB91-007F4EF89576}">
+  <dimension ref="A1:O2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+    <row ht="28.8" r="1" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1439,7 +1446,7 @@
         <v>22</v>
       </c>
       <c r="B2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -1473,16 +1480,16 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{28EE865A-189F-47E2-B372-099EB34B0721}">
-  <dimension ref="A1:N2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{28EE865A-189F-47E2-B372-099EB34B0721}">
+  <dimension ref="A1:O2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+    <row ht="28.8" r="1" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1531,7 +1538,7 @@
         <v>22</v>
       </c>
       <c r="B2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -1565,16 +1572,16 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E6E76688-C590-48CE-8843-48B79B2A30B7}">
-  <dimension ref="A1:N2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E6E76688-C590-48CE-8843-48B79B2A30B7}">
+  <dimension ref="A1:O2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+    <row ht="28.8" r="1" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1640,7 +1647,7 @@
         <v>30</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="L2" s="1"/>
       <c r="M2" s="1" t="s">
@@ -1651,16 +1658,16 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B29E0A75-769C-43A6-A3D3-703A1A1AFA44}">
-  <dimension ref="A1:N2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B29E0A75-769C-43A6-A3D3-703A1A1AFA44}">
+  <dimension ref="A1:O2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+    <row ht="28.8" r="1" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1709,7 +1716,7 @@
         <v>22</v>
       </c>
       <c r="B2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -1743,16 +1750,16 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:N2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:O2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+    <row ht="28.8" r="1" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1801,7 +1808,7 @@
         <v>22</v>
       </c>
       <c r="B2" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -1835,7 +1842,7 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
   <headerFooter>
     <oddFooter xml:space="preserve">&amp;C_x000D_&amp;1#&amp;"Calibri"&amp;10&amp;K000000 Public </oddFooter>
   </headerFooter>
@@ -1843,14 +1850,14 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2B2AA229-8633-483E-A009-0064BA327142}">
-  <dimension ref="A1:N2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2B2AA229-8633-483E-A009-0064BA327142}">
+  <dimension ref="A1:O2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="3" max="3" width="27.77734375" customWidth="1" collapsed="1"/>
+    <col min="3" max="3" customWidth="true" width="27.77734375" collapsed="true"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+    <row ht="28.8" r="1" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1899,7 +1906,7 @@
         <v>22</v>
       </c>
       <c r="B2" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -1935,16 +1942,16 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E49D1CA0-9ECE-4C77-A64C-43CA3156CCD7}">
-  <dimension ref="A1:N2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E49D1CA0-9ECE-4C77-A64C-43CA3156CCD7}">
+  <dimension ref="A1:O2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+    <row ht="28.8" r="1" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1994,7 +2001,7 @@
         <v>14</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>57</v>
+        <v>41</v>
       </c>
       <c r="F2" s="1" t="s">
         <v>20</v>
@@ -2021,16 +2028,16 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EF4DDCDE-4C11-464F-9492-FC8FE5D5A265}">
-  <dimension ref="A1:N2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EF4DDCDE-4C11-464F-9492-FC8FE5D5A265}">
+  <dimension ref="A1:O2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+    <row ht="28.8" r="1" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2076,10 +2083,10 @@
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="B2" t="s">
-        <v>41</v>
+        <v>56</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -2113,16 +2120,16 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{61EC5E6A-6755-4451-A097-7A8CEE1F522B}">
-  <dimension ref="A1:N2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{61EC5E6A-6755-4451-A097-7A8CEE1F522B}">
+  <dimension ref="A1:O2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+    <row ht="28.8" r="1" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2168,10 +2175,10 @@
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="B2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -2205,16 +2212,16 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{46BFFB65-1565-4A34-B0E7-464EF87C75A7}">
-  <dimension ref="A1:N2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{46BFFB65-1565-4A34-B0E7-464EF87C75A7}">
+  <dimension ref="A1:O2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+    <row ht="28.8" r="1" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2263,7 +2270,7 @@
         <v>22</v>
       </c>
       <c r="B2" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -2297,16 +2304,16 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{125BE3DD-7AC0-404A-8C39-EB8ECFFFBDDD}">
-  <dimension ref="A1:N2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{125BE3DD-7AC0-404A-8C39-EB8ECFFFBDDD}">
+  <dimension ref="A1:O2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+    <row ht="28.8" r="1" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2355,7 +2362,7 @@
         <v>22</v>
       </c>
       <c r="B2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -2389,6 +2396,6 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
 </file>
--- a/KatalonData/BWPBootstrapData/BWPCCData.xlsx
+++ b/KatalonData/BWPBootstrapData/BWPCCData.xlsx
@@ -55,7 +55,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="499" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="675" uniqueCount="104">
   <si>
     <t>Result</t>
   </si>
@@ -235,6 +235,138 @@
   </si>
   <si>
     <t>Mon Jan 19 20:07:13 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed May 06 21:56:50 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed May 06 21:57:13 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed May 06 21:57:33 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed May 06 21:57:54 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed May 06 21:59:27 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed May 06 22:05:15 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed May 06 22:07:23 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed May 06 22:09:55 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed May 06 22:12:10 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed May 06 22:13:44 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed May 06 22:15:18 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed May 06 22:22:09 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed May 06 22:24:42 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed May 06 22:27:22 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed May 06 22:30:00 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed May 06 22:30:32 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed May 06 22:31:01 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed May 06 22:32:27 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed May 06 22:33:54 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed May 06 22:35:24 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed May 06 22:35:56 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed May 06 22:36:28 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed May 06 23:16:24 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed May 06 23:16:48 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed May 06 23:17:11 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed May 06 23:19:14 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed May 06 23:25:44 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed May 06 23:27:12 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed May 06 23:29:23 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed May 06 23:32:04 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed May 06 23:45:51 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed May 06 23:47:18 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed May 06 23:50:37 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed May 06 23:52:56 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed May 06 23:58:50 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu May 07 00:01:44 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu May 07 00:02:31 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu May 07 00:03:58 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu May 07 00:05:31 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu May 07 00:06:00 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu May 07 00:08:05 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu May 07 00:09:40 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu May 07 00:10:11 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu May 07 00:10:59 IST 2026</t>
   </si>
 </sst>
 </file>
@@ -710,7 +842,7 @@
         <v>22</v>
       </c>
       <c r="B2" t="s">
-        <v>53</v>
+        <v>101</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -802,7 +934,7 @@
         <v>22</v>
       </c>
       <c r="B2" t="s">
-        <v>59</v>
+        <v>91</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -894,7 +1026,7 @@
         <v>22</v>
       </c>
       <c r="B2" t="s">
-        <v>42</v>
+        <v>84</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -986,7 +1118,7 @@
         <v>22</v>
       </c>
       <c r="B2" t="s">
-        <v>43</v>
+        <v>85</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -1170,7 +1302,7 @@
         <v>22</v>
       </c>
       <c r="B2" t="s">
-        <v>44</v>
+        <v>87</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -1262,7 +1394,7 @@
         <v>22</v>
       </c>
       <c r="B2" t="s">
-        <v>45</v>
+        <v>88</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -1354,7 +1486,7 @@
         <v>22</v>
       </c>
       <c r="B2" t="s">
-        <v>46</v>
+        <v>89</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -1446,7 +1578,7 @@
         <v>22</v>
       </c>
       <c r="B2" t="s">
-        <v>48</v>
+        <v>92</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -1538,7 +1670,7 @@
         <v>22</v>
       </c>
       <c r="B2" t="s">
-        <v>49</v>
+        <v>93</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -1716,7 +1848,7 @@
         <v>22</v>
       </c>
       <c r="B2" t="s">
-        <v>50</v>
+        <v>94</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -1808,7 +1940,7 @@
         <v>22</v>
       </c>
       <c r="B2" t="s">
-        <v>52</v>
+        <v>98</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -1906,7 +2038,7 @@
         <v>22</v>
       </c>
       <c r="B2" t="s">
-        <v>54</v>
+        <v>102</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -2083,10 +2215,10 @@
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="B2" t="s">
-        <v>56</v>
+        <v>82</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -2175,10 +2307,10 @@
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="B2" t="s">
-        <v>57</v>
+        <v>83</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -2270,7 +2402,7 @@
         <v>22</v>
       </c>
       <c r="B2" t="s">
-        <v>55</v>
+        <v>103</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -2362,7 +2494,7 @@
         <v>22</v>
       </c>
       <c r="B2" t="s">
-        <v>51</v>
+        <v>95</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">

--- a/KatalonData/BWPBootstrapData/BWPCCData.xlsx
+++ b/KatalonData/BWPBootstrapData/BWPCCData.xlsx
@@ -55,7 +55,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="675" uniqueCount="104">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="815" uniqueCount="139">
   <si>
     <t>Result</t>
   </si>
@@ -367,6 +367,111 @@
   </si>
   <si>
     <t>Thu May 07 00:10:59 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Jun 08 23:57:20 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Jun 08 23:57:42 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Jun 08 23:58:04 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Jun 08 23:59:29 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Jun 08 23:59:54 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jun 09 00:05:07 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jun 09 00:07:04 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jun 09 00:09:14 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jun 09 00:11:26 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jun 09 00:12:53 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jun 09 00:14:49 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jun 09 00:19:20 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jun 09 00:22:07 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jun 09 00:24:36 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jun 09 00:25:09 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jun 09 00:25:39 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jun 09 00:26:07 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jun 09 00:27:37 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jun 09 00:28:09 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jun 09 00:58:13 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jun 09 00:58:36 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jun 09 00:58:58 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jun 09 01:00:52 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jun 09 01:07:34 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jun 09 01:09:40 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jun 09 01:11:58 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jun 09 01:18:59 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jun 09 01:21:11 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jun 09 01:24:02 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jun 09 01:26:55 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jun 09 01:29:57 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jun 09 01:30:32 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jun 09 01:31:09 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jun 09 01:31:41 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jun 09 01:32:14 IST 2026</t>
   </si>
 </sst>
 </file>
@@ -842,7 +947,7 @@
         <v>22</v>
       </c>
       <c r="B2" t="s">
-        <v>101</v>
+        <v>136</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -934,7 +1039,7 @@
         <v>22</v>
       </c>
       <c r="B2" t="s">
-        <v>91</v>
+        <v>130</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -1026,7 +1131,7 @@
         <v>22</v>
       </c>
       <c r="B2" t="s">
-        <v>84</v>
+        <v>125</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -1118,7 +1223,7 @@
         <v>22</v>
       </c>
       <c r="B2" t="s">
-        <v>85</v>
+        <v>126</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -1302,7 +1407,7 @@
         <v>22</v>
       </c>
       <c r="B2" t="s">
-        <v>87</v>
+        <v>127</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -1394,7 +1499,7 @@
         <v>22</v>
       </c>
       <c r="B2" t="s">
-        <v>88</v>
+        <v>128</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -1486,7 +1591,7 @@
         <v>22</v>
       </c>
       <c r="B2" t="s">
-        <v>89</v>
+        <v>129</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -1578,7 +1683,7 @@
         <v>22</v>
       </c>
       <c r="B2" t="s">
-        <v>92</v>
+        <v>131</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -1670,7 +1775,7 @@
         <v>22</v>
       </c>
       <c r="B2" t="s">
-        <v>93</v>
+        <v>132</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -1848,7 +1953,7 @@
         <v>22</v>
       </c>
       <c r="B2" t="s">
-        <v>94</v>
+        <v>133</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -1940,7 +2045,7 @@
         <v>22</v>
       </c>
       <c r="B2" t="s">
-        <v>98</v>
+        <v>135</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -2038,7 +2143,7 @@
         <v>22</v>
       </c>
       <c r="B2" t="s">
-        <v>102</v>
+        <v>137</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -2218,7 +2323,7 @@
         <v>22</v>
       </c>
       <c r="B2" t="s">
-        <v>82</v>
+        <v>123</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -2310,7 +2415,7 @@
         <v>22</v>
       </c>
       <c r="B2" t="s">
-        <v>83</v>
+        <v>124</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -2402,7 +2507,7 @@
         <v>22</v>
       </c>
       <c r="B2" t="s">
-        <v>103</v>
+        <v>138</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -2494,7 +2599,7 @@
         <v>22</v>
       </c>
       <c r="B2" t="s">
-        <v>95</v>
+        <v>134</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
